--- a/matlab/common/coeffIDSP_Ar.xlsx
+++ b/matlab/common/coeffIDSP_Ar.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rsomeya/Documents/lab/matlab/common/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1F297E-CBFB-F24E-A61C-7108C947A42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCD7FF2-8CBF-7D44-A0CA-A53F4C83AE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="1180" windowWidth="27900" windowHeight="16740" xr2:uid="{3D85D6BD-1CF2-2E45-BE2A-4C8957B87EBE}"/>
+    <workbookView xWindow="3940" yWindow="960" windowWidth="25460" windowHeight="16740" xr2:uid="{3D85D6BD-1CF2-2E45-BE2A-4C8957B87EBE}"/>
   </bookViews>
   <sheets>
-    <sheet name="230807" sheetId="5" r:id="rId1"/>
-    <sheet name="230807_old" sheetId="4" r:id="rId2"/>
-    <sheet name="230521" sheetId="1" r:id="rId3"/>
-    <sheet name="230303" sheetId="2" r:id="rId4"/>
+    <sheet name="240607" sheetId="6" r:id="rId1"/>
+    <sheet name="230807" sheetId="5" r:id="rId2"/>
+    <sheet name="230807_old" sheetId="4" r:id="rId3"/>
+    <sheet name="230521" sheetId="1" r:id="rId4"/>
+    <sheet name="230303" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
   <si>
     <t>ch</t>
     <phoneticPr fontId="1"/>
@@ -69,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,6 +83,14 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -108,8 +117,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -130,9 +142,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -170,7 +182,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -276,7 +288,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -418,13 +430,604 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9A1825-9AD1-1642-97E3-02193ABDA08D}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>660.11419999999998</v>
+      </c>
+      <c r="C2">
+        <v>781.72029999999995</v>
+      </c>
+      <c r="D2">
+        <v>4.2209559999999997E-3</v>
+      </c>
+      <c r="E2">
+        <v>19.48563</v>
+      </c>
+      <c r="F2">
+        <v>96.071749999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>617.93290000000002</v>
+      </c>
+      <c r="C3">
+        <v>784.92660000000001</v>
+      </c>
+      <c r="D3">
+        <v>4.2129450000000001E-3</v>
+      </c>
+      <c r="E3">
+        <v>16.681519999999999</v>
+      </c>
+      <c r="F3">
+        <v>26.561109999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>594.80830000000003</v>
+      </c>
+      <c r="C4">
+        <v>785.46320000000003</v>
+      </c>
+      <c r="D4">
+        <v>4.2187869999999999E-3</v>
+      </c>
+      <c r="E4">
+        <v>19.890250000000002</v>
+      </c>
+      <c r="F4">
+        <v>36.411459999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>573.42970000000003</v>
+      </c>
+      <c r="C5">
+        <v>784.17719999999997</v>
+      </c>
+      <c r="D5">
+        <v>4.214219E-3</v>
+      </c>
+      <c r="E5">
+        <v>17.632300000000001</v>
+      </c>
+      <c r="F5">
+        <v>22.030660000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>486.3664</v>
+      </c>
+      <c r="C6">
+        <v>791.2894</v>
+      </c>
+      <c r="D6">
+        <v>4.2157510000000002E-3</v>
+      </c>
+      <c r="E6">
+        <v>15.25231</v>
+      </c>
+      <c r="F6">
+        <v>48.253570000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>465.25200000000001</v>
+      </c>
+      <c r="C7">
+        <v>786.72649999999999</v>
+      </c>
+      <c r="D7">
+        <v>4.2209669999999999E-3</v>
+      </c>
+      <c r="E7">
+        <v>15.607189999999999</v>
+      </c>
+      <c r="F7">
+        <v>48.234290000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>421.64190000000002</v>
+      </c>
+      <c r="C8">
+        <v>787.47439999999995</v>
+      </c>
+      <c r="D8">
+        <v>4.20931E-3</v>
+      </c>
+      <c r="E8">
+        <v>14.45847</v>
+      </c>
+      <c r="F8">
+        <v>18.255990000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>376.53539999999998</v>
+      </c>
+      <c r="C9">
+        <v>785.68209999999999</v>
+      </c>
+      <c r="D9">
+        <v>4.2130600000000002E-3</v>
+      </c>
+      <c r="E9">
+        <v>14.47635</v>
+      </c>
+      <c r="F9">
+        <v>27.255189999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <v>203.78569999999999</v>
+      </c>
+      <c r="C10">
+        <v>788.32839999999999</v>
+      </c>
+      <c r="D10">
+        <v>4.2214180000000002E-3</v>
+      </c>
+      <c r="E10">
+        <v>14.50874</v>
+      </c>
+      <c r="F10">
+        <v>54.132150000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>27</v>
+      </c>
+      <c r="B11">
+        <v>181.5668</v>
+      </c>
+      <c r="C11">
+        <v>786.12929999999994</v>
+      </c>
+      <c r="D11">
+        <v>4.2241199999999996E-3</v>
+      </c>
+      <c r="E11">
+        <v>13.42835</v>
+      </c>
+      <c r="F11">
+        <v>45.743920000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>28</v>
+      </c>
+      <c r="B12">
+        <v>157.7704</v>
+      </c>
+      <c r="C12">
+        <v>782.75170000000003</v>
+      </c>
+      <c r="D12">
+        <v>4.2235279999999998E-3</v>
+      </c>
+      <c r="E12">
+        <v>14.66803</v>
+      </c>
+      <c r="F12">
+        <v>93.485590000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>29</v>
+      </c>
+      <c r="B13">
+        <v>137.02930000000001</v>
+      </c>
+      <c r="C13">
+        <v>781.63369999999998</v>
+      </c>
+      <c r="D13">
+        <v>4.221687E-3</v>
+      </c>
+      <c r="E13">
+        <v>14.179740000000001</v>
+      </c>
+      <c r="F13">
+        <v>30.436599999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>66</v>
+      </c>
+      <c r="B14">
+        <v>731.59220000000005</v>
+      </c>
+      <c r="C14">
+        <v>289.10669999999999</v>
+      </c>
+      <c r="D14">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E14">
+        <v>17.470369999999999</v>
+      </c>
+      <c r="F14">
+        <v>18.477699999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>67</v>
+      </c>
+      <c r="B15">
+        <v>708.89639999999997</v>
+      </c>
+      <c r="C15">
+        <v>288.86540000000002</v>
+      </c>
+      <c r="D15">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E15">
+        <v>15.62514</v>
+      </c>
+      <c r="F15">
+        <v>26.39386</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>69</v>
+      </c>
+      <c r="B16">
+        <v>668.90650000000005</v>
+      </c>
+      <c r="C16">
+        <v>292.81830000000002</v>
+      </c>
+      <c r="D16">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E16">
+        <v>14.890549999999999</v>
+      </c>
+      <c r="F16">
+        <v>12.07747</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>70</v>
+      </c>
+      <c r="B17">
+        <v>647.04629999999997</v>
+      </c>
+      <c r="C17">
+        <v>290.0838</v>
+      </c>
+      <c r="D17">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E17">
+        <v>18.71528</v>
+      </c>
+      <c r="F17">
+        <v>18.398430000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>71</v>
+      </c>
+      <c r="B18">
+        <v>626.01120000000003</v>
+      </c>
+      <c r="C18">
+        <v>292.29599999999999</v>
+      </c>
+      <c r="D18">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E18">
+        <v>17.37454</v>
+      </c>
+      <c r="F18">
+        <v>25.800650000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>72</v>
+      </c>
+      <c r="B19">
+        <v>603.04169999999999</v>
+      </c>
+      <c r="C19">
+        <v>287.15370000000001</v>
+      </c>
+      <c r="D19">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E19">
+        <v>19.82469</v>
+      </c>
+      <c r="F19">
+        <v>31.848780000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>73</v>
+      </c>
+      <c r="B20">
+        <v>583.43200000000002</v>
+      </c>
+      <c r="C20">
+        <v>292.51909999999998</v>
+      </c>
+      <c r="D20">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E20">
+        <v>21.69472</v>
+      </c>
+      <c r="F20">
+        <v>27.35877</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>74</v>
+      </c>
+      <c r="B21">
+        <v>559.87900000000002</v>
+      </c>
+      <c r="C21">
+        <v>293.06819999999999</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E21">
+        <v>19.852139999999999</v>
+      </c>
+      <c r="F21">
+        <v>40.763420000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22">
+        <v>356.62700000000001</v>
+      </c>
+      <c r="C22">
+        <v>790.10419999999999</v>
+      </c>
+      <c r="D22">
+        <v>4.2207859999999998E-3</v>
+      </c>
+      <c r="E22">
+        <v>16.649239999999999</v>
+      </c>
+      <c r="F22">
+        <v>37.786969999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>335.41300000000001</v>
+      </c>
+      <c r="C23">
+        <v>793.18920000000003</v>
+      </c>
+      <c r="D23">
+        <v>4.2181509999999998E-3</v>
+      </c>
+      <c r="E23">
+        <v>13.97522</v>
+      </c>
+      <c r="F23">
+        <v>84.217380000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>286.95370000000003</v>
+      </c>
+      <c r="C24">
+        <v>785.41409999999996</v>
+      </c>
+      <c r="D24">
+        <v>4.2103879999999998E-3</v>
+      </c>
+      <c r="E24">
+        <v>17.372</v>
+      </c>
+      <c r="F24">
+        <v>12.393520000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>266.3449</v>
+      </c>
+      <c r="C25">
+        <v>786.61710000000005</v>
+      </c>
+      <c r="D25">
+        <v>4.2166979999999996E-3</v>
+      </c>
+      <c r="E25">
+        <v>17.01193</v>
+      </c>
+      <c r="F25">
+        <v>54.894410000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>76</v>
+      </c>
+      <c r="B26">
+        <v>514.36699999999996</v>
+      </c>
+      <c r="C26">
+        <v>290.2278</v>
+      </c>
+      <c r="D26" s="1">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E26">
+        <v>16.475639999999999</v>
+      </c>
+      <c r="F26">
+        <v>31.028559999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>77</v>
+      </c>
+      <c r="B27">
+        <v>495.56450000000001</v>
+      </c>
+      <c r="C27">
+        <v>295.63189999999997</v>
+      </c>
+      <c r="D27" s="1">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E27">
+        <v>17.247350000000001</v>
+      </c>
+      <c r="F27">
+        <v>15.714600000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>78</v>
+      </c>
+      <c r="B28">
+        <v>470.42009999999999</v>
+      </c>
+      <c r="C28">
+        <v>293.05630000000002</v>
+      </c>
+      <c r="D28" s="1">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E28">
+        <v>19.9878</v>
+      </c>
+      <c r="F28">
+        <v>52.286050000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>79</v>
+      </c>
+      <c r="B29">
+        <v>449.5471</v>
+      </c>
+      <c r="C29">
+        <v>292.55380000000002</v>
+      </c>
+      <c r="D29" s="1">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="E29">
+        <v>22.33043</v>
+      </c>
+      <c r="F29">
+        <v>24.526489999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0114F5-3518-E841-95CC-F78B161415E4}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
@@ -1015,7 +1618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BD62D1-155F-3C4F-B35A-79BA5EDC0996}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
@@ -1606,7 +2209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F5DD6-39DE-C74E-ACBA-99DDB9B2D7DB}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
@@ -2197,7 +2800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640AE379-DA8E-5643-98AC-E969B38B8493}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
